--- a/business_forms/040_product_branding_performance_report_form--business_forms.xlsx
+++ b/business_forms/040_product_branding_performance_report_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'brand_name',_'value':_'brand_name'}</t>
+          <t>brand_name</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Brand Name', 'value': 'brand_name'}</t>
+          <t>Brand Name</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'product_name',_'value':_'product_name'}</t>
+          <t>product_name</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Product Name', 'value': 'product_name'}</t>
+          <t>Product Name</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'tagline',_'value':_'tagline'}</t>
+          <t>tagline</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Tagline', 'value': 'tagline'}</t>
+          <t>Tagline</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'logo',_'value':_'logo'}</t>
+          <t>logo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'Logo', 'value': 'logo'}</t>
+          <t>Logo</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_"women's",_'value':_'women'}</t>
+          <t>women's</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': "Women's", 'value': 'women'}</t>
+          <t>Women's</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_16,_'label':_"men's",_'value':_'men'}</t>
+          <t>men's</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 16, 'label': "Men's", 'value': 'men'}</t>
+          <t>Men's</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_17,_'label':_"kids'",_'value':_'kids'}</t>
+          <t>kids'</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 17, 'label': "Kids'", 'value': 'kids'}</t>
+          <t>Kids'</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_18,_'label':_'unisex',_'value':_'unisex'}</t>
+          <t>unisex</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 18, 'label': 'Unisex', 'value': 'unisex'}</t>
+          <t>Unisex</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_19,_'label':_'business',_'value':_'business'}</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 19, 'label': 'Business', 'value': 'business'}</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'social_media',_'value':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'Social Media', 'value': 'social_media'}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'Email', 'value': 'email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'in-store',_'value':_'in_store'}</t>
+          <t>in-store</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'In-store', 'value': 'in_store'}</t>
+          <t>In-store</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_23,_'label':_'online',_'value':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 23, 'label': 'Online', 'value': 'online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_24,_'label':_'offline',_'value':_'offline'}</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 24, 'label': 'Offline', 'value': 'offline'}</t>
+          <t>Offline</t>
         </is>
       </c>
     </row>
